--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -488,37 +488,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Momin Hyat Khan</t>
+          <t>Zeeshan Zahoor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mominhyatkhandeveloper@gmail.com</t>
+          <t>zeeshanzahoor409@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>03345674415</t>
+          <t>+923421905266</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mominhyatkhan</t>
+          <t>https://www.linkedin.com/in/zeeshan-zahoor-220b0b130</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://github.com/mominhyatkhan</t>
+          <t>https://github.com/zeeshanshaanu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, typescript, html, tailwind css, redux, css, react</t>
+          <t>css, javascript, typescript, git, material ui, tailwind css, redux, react.js, react</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -534,40 +534,44 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>react.js, api's integration, react router, rest api</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Zeeshan Zahoor</t>
+          <t>Momin Hyat Khan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zeeshanzahoor409@gmail.com</t>
+          <t>mominhyatkhandeveloper@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+923421905266</t>
+          <t>03345674415</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/zeeshan-zahoor-220b0b130</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>https://linkedin.com/in/mominhyatkhan</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://github.com/mominhyatkhan</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>material ui, redux, javascript, typescript, css, react, git, react.js, tailwind css</t>
+          <t>javascript, material ui, html, typescript, git, tailwind css, redux, react, css</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>4 years 0 months</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -576,14 +580,14 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>85.69</v>
+        <v>87.69</v>
       </c>
       <c r="J3" t="n">
         <v>2</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>api's integration, react router, html, rest api</t>
+          <t>api's integration, rest api, react router, react.js</t>
         </is>
       </c>
     </row>
@@ -608,10 +612,14 @@
           <t>https://www.linkedin.com/in/zeeshan-zahoor-220b0b130</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://github.com/zeeshanshaanu</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>material ui, redux, javascript, typescript, css, react, git, react.js, tailwind css</t>
+          <t>css, javascript, typescript, git, material ui, tailwind css, redux, react.js, react</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -625,14 +633,14 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>85.69</v>
+        <v>87.69</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>api's integration, react router, html, rest api</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -664,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>redux, javascript, typescript, css, react, git, react.js, tailwind css</t>
+          <t>css, javascript, typescript, git, tailwind css, redux, react.js, react</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -685,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>material ui, api's integration, react router, html, rest api</t>
+          <t>material ui, api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -712,12 +720,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>http://github.com/ayazcoder</t>
+          <t>https://github.com/ayazcoder</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, tailwind css, react, css</t>
+          <t>javascript, material ui, git, tailwind css, react, css, react.js</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -738,7 +746,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>typescript, api's integration, react router, html, redux, rest api</t>
+          <t>api's integration, typescript, html, redux, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -762,7 +770,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, typescript, tailwind css, css, react</t>
+          <t>javascript, material ui, typescript, git, tailwind css, react, css, react.js</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -783,7 +791,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>api's integration, react router, html, redux, rest api</t>
+          <t>api's integration, html, redux, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -807,7 +815,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>javascript, git, react.js, html, tailwind css, css, react</t>
+          <t>javascript, html, git, tailwind css, react, css, react.js</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -828,7 +836,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>material ui, typescript, api's integration, react router, redux, rest api</t>
+          <t>material ui, api's integration, typescript, redux, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -852,7 +860,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>javascript, react.js, html, redux, css, react</t>
+          <t>javascript, html, redux, react, css, react.js</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -873,7 +881,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>material ui, git, typescript, api's integration, react router, tailwind css, rest api</t>
+          <t>material ui, api's integration, typescript, git, tailwind css, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -918,7 +926,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>material ui, react.js, typescript, api's integration, react router, html, tailwind css, redux, css, react</t>
+          <t>material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
@@ -963,7 +971,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>material ui, react.js, typescript, api's integration, react router, html, tailwind css, redux, css, react</t>
+          <t>material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1016,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>material ui, javascript, react.js, typescript, api's integration, react router, html, tailwind css, redux, css, react</t>
+          <t>javascript, material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1039,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://github.com/</t>
+          <t>https://github.com/model</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1057,7 +1065,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, typescript, api's integration, react router, html, tailwind css, redux, css, react</t>
+          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1088,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://github.com/</t>
+          <t>https://github.com/PROFILE</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -1102,24 +1110,24 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, typescript, api's integration, react router, html, tailwind css, redux, rest api, css, react</t>
+          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Robin Doe</t>
+          <t>Tanjiro Bhatia</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fobin.doe@example.com</t>
+          <t>Tanjiro.bhatia67@gmail.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>123451234567090</t>
+          <t>9923312341</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1127,7 +1135,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>8 years 6 months</t>
+          <t>6 years 0 months</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1143,24 +1151,20 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, typescript, api's integration, react router, html, tailwind css, redux, rest api, css, react</t>
+          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tanjiro Bhatia</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Tanjiro.bhatia67@gmail.com</t>
-        </is>
-      </c>
+          <t>Robin Doe</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9923312341</t>
+          <t>123451234567090</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1168,7 +1172,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6 years 0 months</t>
+          <t>8 years 6 months</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1177,14 +1181,14 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>material ui, javascript, git, react.js, typescript, api's integration, react router, html, tailwind css, redux, rest api, css, react</t>
+          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>css, javascript, typescript, git, material ui, tailwind css, redux, react.js, react</t>
+          <t>redux, javascript, react, tailwind css, git, typescript, material ui, css, react.js</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>html, api's integration, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>javascript, material ui, html, typescript, git, tailwind css, redux, react, css</t>
+          <t>html, material ui, css, git, tailwind css, redux, javascript, typescript, react</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>api's integration, rest api, react router, react.js</t>
+          <t>api's integration, rest api, react.js, react router</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>css, javascript, typescript, git, material ui, tailwind css, redux, react.js, react</t>
+          <t>redux, javascript, react, tailwind css, git, typescript, material ui, css, react.js</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>html, api's integration, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>css, javascript, typescript, git, tailwind css, redux, react.js, react</t>
+          <t>redux, javascript, react, tailwind css, typescript, git, css, react.js</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>material ui, api's integration, html, rest api, react router</t>
+          <t>html, api's integration, material ui, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>javascript, material ui, git, tailwind css, react, css, react.js</t>
+          <t>material ui, css, tailwind css, react.js, javascript, git, react</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>api's integration, typescript, html, redux, rest api, react router</t>
+          <t>html, api's integration, rest api, redux, typescript, react router</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>javascript, material ui, typescript, git, tailwind css, react, css, react.js</t>
+          <t>material ui, css, tailwind css, react.js, javascript, git, typescript, react</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>api's integration, html, redux, rest api, react router</t>
+          <t>html, api's integration, rest api, redux, react router</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>javascript, html, git, tailwind css, react, css, react.js</t>
+          <t>html, css, tailwind css, react.js, javascript, git, react</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>material ui, api's integration, typescript, redux, rest api, react router</t>
+          <t>api's integration, material ui, rest api, redux, typescript, react router</t>
         </is>
       </c>
     </row>
@@ -860,7 +860,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>javascript, html, redux, react, css, react.js</t>
+          <t>html, css, redux, react.js, javascript, react</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>material ui, api's integration, typescript, git, tailwind css, rest api, react router</t>
+          <t>api's integration, material ui, tailwind css, rest api, git, typescript, react router</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>javascript, git, rest api</t>
+          <t>rest api, javascript, git</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>javascript, git, rest api</t>
+          <t>rest api, javascript, git</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>git, rest api</t>
+          <t>rest api, git</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>javascript, material ui, api's integration, typescript, html, tailwind css, redux, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, javascript, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, javascript, git, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>javascript, material ui, api's integration, typescript, html, git, tailwind css, redux, rest api, react, css, react router, react.js</t>
+          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>redux, javascript, react, tailwind css, git, typescript, material ui, css, react.js</t>
+          <t>react, material ui, javascript, git, css, redux, tailwind css, typescript, react.js</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>html, api's integration, rest api, react router</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>html, material ui, css, git, tailwind css, redux, javascript, typescript, react</t>
+          <t>javascript, tailwind css, git, html, react, typescript, redux, css, material ui</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>redux, javascript, react, tailwind css, git, typescript, material ui, css, react.js</t>
+          <t>react, material ui, javascript, git, css, redux, tailwind css, typescript, react.js</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>html, api's integration, rest api, react router</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>redux, javascript, react, tailwind css, typescript, git, css, react.js</t>
+          <t>react, javascript, git, css, redux, tailwind css, typescript, react.js</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, rest api, react router</t>
+          <t>api's integration, html, rest api, material ui, react router</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>material ui, css, tailwind css, react.js, javascript, git, react</t>
+          <t>javascript, tailwind css, git, react, css, material ui, react.js</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>html, api's integration, rest api, redux, typescript, react router</t>
+          <t>api's integration, html, typescript, redux, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>material ui, css, tailwind css, react.js, javascript, git, typescript, react</t>
+          <t>javascript, tailwind css, git, css, typescript, react, material ui, react.js</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -791,36 +791,44 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>html, api's integration, rest api, redux, react router</t>
+          <t>api's integration, html, redux, rest api, react router</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>About Me</t>
+          <t>Sami Ullah Khan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mtahayasin07@gmail.com</t>
+          <t>samikhaan7814@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>03406991719</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+          <t>+923443777814</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sami-khan-111678169</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://github.com/mr-samikhan</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>html, css, tailwind css, react.js, javascript, git, react</t>
+          <t>tailwind css, api's integration, react, redux, css, material ui</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3 years 6 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -829,88 +837,88 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>76.54000000000001</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>api's integration, material ui, rest api, redux, typescript, react router</t>
+          <t>javascript, git, html, typescript, rest api, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Resumemuhammadwaqas3Y</t>
+          <t>About Me</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mwbkkj@gmail.com</t>
+          <t>mtahayasin07@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03126318724</t>
+          <t>03406991719</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>html, css, redux, react.js, javascript, react</t>
+          <t>javascript, tailwind css, git, html, react, css, react.js</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>5 years 6 months</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>73.45999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="J9" t="n">
         <v>9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>api's integration, material ui, tailwind css, rest api, git, typescript, react router</t>
+          <t>api's integration, typescript, redux, rest api, material ui, react router</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rahul Mishra</t>
+          <t>Resumemuhammadwaqas3Y</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rahul.mishra@gmail.com</t>
+          <t>Mwbkkj@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>03126318724</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>rest api, javascript, git</t>
+          <t>javascript, html, react, redux, css, react.js</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -919,14 +927,14 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>64.23</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, typescript, react router, react</t>
+          <t>git, tailwind css, api's integration, typescript, rest api, material ui, react router</t>
         </is>
       </c>
     </row>
@@ -950,7 +958,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>rest api, javascript, git</t>
+          <t>javascript, git, rest api</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -967,23 +975,23 @@
         <v>64.23</v>
       </c>
       <c r="J11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, typescript, react router, react</t>
+          <t>tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Shubham Mishra</t>
+          <t>Rahul Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>shubham.mishra@gmail.com</t>
+          <t>rahul.mishra@gmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -995,106 +1003,114 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>rest api, git</t>
+          <t>javascript, git, rest api</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7 years 0 months</t>
+          <t>4 years 0 months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>61.15</v>
+        <v>64.23</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, javascript, typescript, react router, react</t>
+          <t>tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Kamado Associate Lead</t>
+          <t>Muhammad Shayan</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hello.ineuron@gmail.com</t>
+          <t>kshayan091@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9923312341</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://github.com/model</t>
-        </is>
-      </c>
+          <t>+923168104861</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shayan-khan20</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>rest api</t>
+          <t>javascript, typescript, react, redux, material ui</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6 years 0 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>high school</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>60.08</v>
+        <v>63.38</v>
       </c>
       <c r="J13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, redux, react.js, javascript, git, typescript, react router, react</t>
+          <t>git, tailwind css, api's integration, html, css, rest api, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Naruto Uzumaki</t>
+          <t>Biswajit Khetan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hello.ineuron@gmail.com</t>
+          <t>bisjwa1445@gmail.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9923312341</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>+91987654321</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/11i/</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://github.com/PROFILE</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>https://github.com/AnkitDB9</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>rest api</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>4 years 8 months</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1103,92 +1119,284 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>57</v>
+        <v>63.08</v>
       </c>
       <c r="J14" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
+          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Tanjiro Bhatia</t>
+          <t>Juan Jose Carin</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tanjiro.bhatia67@gmail.com</t>
+          <t>juanjose.carin@gmail.com</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9923312341</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>940416503364590</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/juanjosecarin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://github.com/juanjocarin/W261-Machine-Learning-At-Scale/blob/master/Week07-MrJob/MIDS-W261-2015-HWK-Week07-CarinLlopSatpati-groupZ.ipynb</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>git</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6 years 0 months</t>
+          <t>5 years 1 months</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>master</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>55</v>
+        <v>63.08</v>
       </c>
       <c r="J15" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
+          <t>javascript, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Robin Doe</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>Shubham Mishra</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shubham.mishra@gmail.com</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>123451234567090</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>git, rest api</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>7 years 0 months</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>javascript, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kamado Associate Lead</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>hello.ineuron@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>9923312341</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://github.com/model</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>rest api</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>6 years 0 months</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Naruto Uzumaki</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>hello.ineuron@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>9923312341</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://github.com/PROFILE</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4 years 0 months</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>57</v>
+      </c>
+      <c r="J18" t="n">
+        <v>31</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Tanjiro Bhatia</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tanjiro.bhatia67@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>9923312341</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>6 years 0 months</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>55</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Robin Doe</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>123451234567090</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>8 years 6 months</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>bachelor</t>
         </is>
       </c>
-      <c r="I16" t="n">
+      <c r="I20" t="n">
         <v>52</v>
       </c>
-      <c r="J16" t="n">
-        <v>31</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>html, api's integration, material ui, css, tailwind css, rest api, redux, react.js, javascript, git, typescript, react router, react</t>
+      <c r="J20" t="n">
+        <v>35</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,37 +488,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Zeeshan Zahoor</t>
+          <t>Momin Hyat Khan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zeeshanzahoor409@gmail.com</t>
+          <t>mominhyatkhandeveloper@gmail.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+923421905266</t>
+          <t>03345674415</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/zeeshan-zahoor-220b0b130</t>
+          <t>https://linkedin.com/in/mominhyatkhan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://github.com/zeeshanshaanu</t>
+          <t>https://github.com/mominhyatkhan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>react, material ui, javascript, git, css, redux, tailwind css, typescript, react.js</t>
+          <t>react, typescript, tailwind css, css, redux, javascript, html, material ui, git</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>4 years 0 months</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -534,44 +534,44 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>api's integration, react.js, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Momin Hyat Khan</t>
+          <t>Zeeshan Zahoor</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mominhyatkhandeveloper@gmail.com</t>
+          <t>zeeshanzahoor409@gmail.com</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>03345674415</t>
+          <t>+923421905266</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/mominhyatkhan</t>
+          <t>https://www.linkedin.com/in/zeeshan-zahoor-220b0b130</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://github.com/mominhyatkhan</t>
+          <t>https://github.com/zeeshanshaanu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, git, html, react, typescript, redux, css, material ui</t>
+          <t>react.js, react, typescript, tailwind css, css, redux, javascript, material ui, git</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>api's integration, rest api, react.js, react router</t>
+          <t>html, api's integration, react router, rest api</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>react, material ui, javascript, git, css, redux, tailwind css, typescript, react.js</t>
+          <t>react.js, react, typescript, tailwind css, css, redux, javascript, material ui, git</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>html, api's integration, react router, rest api</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>react, javascript, git, css, redux, tailwind css, typescript, react.js</t>
+          <t>react.js, react, typescript, tailwind css, css, redux, javascript, git</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,44 +693,40 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, material ui, react router</t>
+          <t>html, api's integration, material ui, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ayaz Khan</t>
+          <t>Resumeabdullahkhan</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>pakistan03479@gmail.com</t>
+          <t>abdullahkh1144@gmail.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+923139131611</t>
+          <t>+923105778487</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://linkedin.com/in/ayazcoder</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://github.com/ayazcoder</t>
-        </is>
-      </c>
+          <t>https://linkedin.com/in/abdullah-khan-0727b0247</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, git, react, css, material ui, react.js</t>
+          <t>react.js, react, typescript, tailwind css, css, redux, javascript, git</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3 years 2 months</t>
+          <t>5 years 0 months</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -739,43 +735,51 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>81.54000000000001</v>
+        <v>82.62</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>api's integration, html, typescript, redux, rest api, react router</t>
+          <t>html, api's integration, material ui, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junaid Akbar</t>
+          <t>Ayaz Khan</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>junaidjojo4@gmail.com</t>
+          <t>pakistan03479@gmail.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+923337661597</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>+923139131611</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/ayazcoder</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://github.com/ayazcoder</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, git, css, typescript, react, material ui, react.js</t>
+          <t>react.js, react, tailwind css, css, javascript, material ui, git</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>3 years 2 months</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -784,46 +788,38 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>79.62</v>
+        <v>81.54000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>api's integration, html, redux, rest api, react router</t>
+          <t>html, api's integration, typescript, redux, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sami Ullah Khan</t>
+          <t>Junaid Akbar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>samikhaan7814@gmail.com</t>
+          <t>junaidjojo4@gmail.com</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+923443777814</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://linkedin.com/in/sami-khan-111678169</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://github.com/mr-samikhan</t>
-        </is>
-      </c>
+          <t>+923337661597</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tailwind css, api's integration, react, redux, css, material ui</t>
+          <t>react, react.js, typescript, material ui, css, git, tailwind css, javascript</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -837,43 +833,51 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>78.45999999999999</v>
+        <v>79.62</v>
       </c>
       <c r="J8" t="n">
         <v>8</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>javascript, git, html, typescript, rest api, react.js, react router</t>
+          <t>html, api's integration, redux, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>About Me</t>
+          <t>Sami Ullah Khan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>mtahayasin07@gmail.com</t>
+          <t>samikhaan7814@gmail.com</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>03406991719</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>+923443777814</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://linkedin.com/in/sami-khan-111678169</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://github.com/mr-samikhan</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, git, html, react, css, react.js</t>
+          <t>api's integration, react, css, redux, material ui, tailwind css</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5 years 6 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -882,83 +886,83 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>76.54000000000001</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>9</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>api's integration, typescript, redux, rest api, material ui, react router</t>
+          <t>html, react.js, typescript, git, react router, javascript, rest api</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Resumemuhammadwaqas3Y</t>
+          <t>About Me</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mwbkkj@gmail.com</t>
+          <t>mtahayasin07@gmail.com</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>03126318724</t>
+          <t>03406991719</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>javascript, html, react, redux, css, react.js</t>
+          <t>html, react, react.js, css, git, tailwind css, javascript</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>5 years 6 months</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>bachelor</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>73.45999999999999</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>git, tailwind css, api's integration, typescript, rest api, material ui, react router</t>
+          <t>api's integration, typescript, material ui, redux, react router, rest api</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shubham Mishra</t>
+          <t>Resumemuhammadwaqas3Y</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>shubham.mishra@gmail.com</t>
+          <t>Mwbkkj@gmail.com</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9876543210</t>
+          <t>03126318724</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>javascript, git, rest api</t>
+          <t>html, react, react.js, css, redux, javascript</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -972,26 +976,26 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>64.23</v>
+        <v>73.45999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+          <t>api's integration, typescript, material ui, git, react router, tailwind css, rest api</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rahul Mishra</t>
+          <t>Shubham Mishra</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rahul.mishra@gmail.com</t>
+          <t>shubham.mishra@gmail.com</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1008,7 +1012,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1020,113 +1024,105 @@
         <v>64.23</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Muhammad Shayan</t>
+          <t>Rahul Mishra</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kshayan091@gmail.com</t>
+          <t>rahul.mishra@gmail.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+923168104861</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/shayan-khan20</t>
-        </is>
-      </c>
+          <t>9876543210</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>javascript, typescript, react, redux, material ui</t>
+          <t>javascript, git, rest api</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3 years 0 months</t>
+          <t>4 years 0 months</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>high school</t>
+          <t>master</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>63.38</v>
+        <v>64.23</v>
       </c>
       <c r="J13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>git, tailwind css, api's integration, html, css, rest api, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Biswajit Khetan</t>
+          <t>Muhammad Shayan</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bisjwa1445@gmail.com</t>
+          <t>kshayan091@gmail.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+91987654321</t>
+          <t>+923168104861</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/11i/</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://github.com/AnkitDB9</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/in/shayan-khan20</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>rest api</t>
+          <t>react, typescript, redux, javascript, material ui</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4 years 8 months</t>
+          <t>3 years 0 months</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>bachelor</t>
+          <t>high school</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>63.08</v>
+        <v>63.38</v>
       </c>
       <c r="J14" t="n">
         <v>20</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+          <t>html, api's integration, react.js, css, git, react router, tailwind css, rest api</t>
         </is>
       </c>
     </row>
@@ -1175,40 +1171,48 @@
         <v>63.08</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css, javascript, rest api</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Shubham Mishra</t>
+          <t>Biswajit Khetan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>shubham.mishra@gmail.com</t>
+          <t>bisjwa1445@gmail.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9876543210</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+          <t>+91987654321</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/11i/</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://github.com/AnkitDB9</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>git, rest api</t>
+          <t>rest api</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7 years 0 months</t>
+          <t>4 years 8 months</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1217,47 +1221,43 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>61.15</v>
+        <v>63.08</v>
       </c>
       <c r="J16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>javascript, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kamado Associate Lead</t>
+          <t>Shubham Mishra</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hello.ineuron@gmail.com</t>
+          <t>shubham.mishra@gmail.com</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>9923312341</t>
+          <t>9876543210</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://github.com/model</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>rest api</t>
+          <t>git, rest api</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6 years 0 months</t>
+          <t>7 years 0 months</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1266,21 +1266,21 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>60.08</v>
+        <v>61.15</v>
       </c>
       <c r="J17" t="n">
         <v>26</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css, javascript</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Naruto Uzumaki</t>
+          <t>Kamado Associate Lead</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1296,13 +1296,17 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://github.com/PROFILE</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>https://github.com/model</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>rest api</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4 years 0 months</t>
+          <t>6 years 0 months</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1311,26 +1315,26 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>57</v>
+        <v>60.08</v>
       </c>
       <c r="J18" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Tanjiro Bhatia</t>
+          <t>Naruto Uzumaki</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tanjiro.bhatia67@gmail.com</t>
+          <t>hello.ineuron@gmail.com</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1339,11 +1343,15 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://github.com/PROFILE</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6 years 0 months</t>
+          <t>4 years 0 months</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1352,27 +1360,31 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J19" t="n">
         <v>33</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Robin Doe</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Tanjiro Bhatia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tanjiro.bhatia67@gmail.com</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>123451234567090</t>
+          <t>9923312341</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1380,23 +1392,60 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
+          <t>6 years 0 months</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>bachelor</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>55</v>
+      </c>
+      <c r="J20" t="n">
+        <v>36</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Robin Doe</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>123451234567090</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>8 years 6 months</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>bachelor</t>
         </is>
       </c>
-      <c r="I20" t="n">
+      <c r="I21" t="n">
         <v>52</v>
       </c>
-      <c r="J20" t="n">
-        <v>35</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>javascript, git, tailwind css, api's integration, html, typescript, react, redux, css, rest api, material ui, react.js, react router</t>
+      <c r="J21" t="n">
+        <v>38</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>react, typescript, tailwind css, css, redux, javascript, html, material ui, git</t>
+          <t>react, typescript, css, material ui, redux, tailwind css, git, html, javascript</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>api's integration, react.js, react router, rest api</t>
+          <t>react router, react.js, api's integration, rest api</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>react.js, react, typescript, tailwind css, css, redux, javascript, material ui, git</t>
+          <t>react, typescript, css, material ui, tailwind css, react.js, git, javascript, redux</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>html, api's integration, react router, rest api</t>
+          <t>react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>react.js, react, typescript, tailwind css, css, redux, javascript, material ui, git</t>
+          <t>react, typescript, css, material ui, tailwind css, react.js, git, javascript, redux</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>html, api's integration, react router, rest api</t>
+          <t>react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>react.js, react, typescript, tailwind css, css, redux, javascript, git</t>
+          <t>react, typescript, css, tailwind css, react.js, git, javascript, redux</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, react router, rest api</t>
+          <t>react router, material ui, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>react.js, react, typescript, tailwind css, css, redux, javascript, git</t>
+          <t>react, typescript, css, redux, tailwind css, react.js, git, javascript</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>html, api's integration, material ui, react router, rest api</t>
+          <t>react router, material ui, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>react.js, react, tailwind css, css, javascript, material ui, git</t>
+          <t>react, css, material ui, tailwind css, react.js, git, javascript</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>html, api's integration, typescript, redux, react router, rest api</t>
+          <t>react router, api's integration, rest api, html, typescript, redux</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>react, react.js, typescript, material ui, css, git, tailwind css, javascript</t>
+          <t>tailwind css, react, react.js, git, material ui, typescript, css, javascript</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>html, api's integration, redux, react router, rest api</t>
+          <t>react router, api's integration, rest api, html, redux</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>api's integration, react, css, redux, material ui, tailwind css</t>
+          <t>redux, tailwind css, react, material ui, api's integration, css</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>html, react.js, typescript, git, react router, javascript, rest api</t>
+          <t>react router, react.js, git, rest api, html, typescript, javascript</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>html, react, react.js, css, git, tailwind css, javascript</t>
+          <t>tailwind css, css, react, react.js, git, html, javascript</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>api's integration, typescript, material ui, redux, react router, rest api</t>
+          <t>react router, material ui, api's integration, rest api, typescript, redux</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>html, react, react.js, css, redux, javascript</t>
+          <t>redux, css, react, react.js, html, javascript</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>api's integration, typescript, material ui, git, react router, tailwind css, rest api</t>
+          <t>tailwind css, react router, git, material ui, api's integration, rest api, typescript</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>javascript, git, rest api</t>
+          <t>git, rest api, javascript</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css</t>
+          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>javascript, git, rest api</t>
+          <t>git, rest api, javascript</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css</t>
+          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>react, typescript, redux, javascript, material ui</t>
+          <t>react, typescript, material ui, javascript, redux</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1118,11 +1118,11 @@
         <v>63.38</v>
       </c>
       <c r="J14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>html, api's integration, react.js, css, git, react router, tailwind css, rest api</t>
+          <t>tailwind css, css, react router, react.js, git, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css, javascript, rest api</t>
+          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript</t>
+          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, redux, react router, tailwind css, javascript</t>
+          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1318,11 +1318,11 @@
         <v>60.08</v>
       </c>
       <c r="J18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript</t>
+          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
+          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
+          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>html, api's integration, react, react.js, typescript, material ui, css, git, redux, react router, tailwind css, javascript, rest api</t>
+          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>react, typescript, css, material ui, redux, tailwind css, git, html, javascript</t>
+          <t>redux, typescript, javascript, css, react, material ui, git, html, tailwind css</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>react router, react.js, api's integration, rest api</t>
+          <t>api's integration, react.js, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>react, typescript, css, material ui, tailwind css, react.js, git, javascript, redux</t>
+          <t>redux, react.js, typescript, javascript, css, react, material ui, git, tailwind css</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>react router, api's integration, rest api, html</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>react, typescript, css, material ui, tailwind css, react.js, git, javascript, redux</t>
+          <t>redux, react.js, typescript, javascript, css, react, material ui, git, tailwind css</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>react router, api's integration, rest api, html</t>
+          <t>api's integration, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>react, typescript, css, tailwind css, react.js, git, javascript, redux</t>
+          <t>redux, react.js, typescript, javascript, css, react, git, tailwind css</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>react router, material ui, api's integration, rest api, html</t>
+          <t>api's integration, html, material ui, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>react, typescript, css, redux, tailwind css, react.js, git, javascript</t>
+          <t>redux, react.js, typescript, javascript, css, react, git, tailwind css</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>react router, material ui, api's integration, rest api, html</t>
+          <t>api's integration, html, material ui, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>react, css, material ui, tailwind css, react.js, git, javascript</t>
+          <t>react.js, javascript, css, react, material ui, git, tailwind css</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>react router, api's integration, rest api, html, typescript, redux</t>
+          <t>api's integration, typescript, redux, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>tailwind css, react, react.js, git, material ui, typescript, css, javascript</t>
+          <t>react.js, git, typescript, react, material ui, javascript, tailwind css, css</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>react router, api's integration, rest api, html, redux</t>
+          <t>api's integration, redux, html, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>redux, tailwind css, react, material ui, api's integration, css</t>
+          <t>api's integration, redux, react, material ui, tailwind css, css</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>react router, react.js, git, rest api, html, typescript, javascript</t>
+          <t>react.js, git, typescript, html, javascript, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>tailwind css, css, react, react.js, git, html, javascript</t>
+          <t>react.js, git, react, html, javascript, tailwind css, css</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>react router, material ui, api's integration, rest api, typescript, redux</t>
+          <t>api's integration, typescript, redux, material ui, rest api, react router</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>redux, css, react, react.js, html, javascript</t>
+          <t>react.js, redux, react, html, javascript, css</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>tailwind css, react router, git, material ui, api's integration, rest api, typescript</t>
+          <t>api's integration, git, typescript, material ui, rest api, react router, tailwind css</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>git, rest api, javascript</t>
+          <t>javascript, rest api, git</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux</t>
+          <t>api's integration, react.js, typescript, redux, react, html, material ui, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>git, rest api, javascript</t>
+          <t>javascript, rest api, git</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux</t>
+          <t>api's integration, react.js, typescript, redux, react, html, material ui, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>react, typescript, material ui, javascript, redux</t>
+          <t>redux, typescript, javascript, react, material ui</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, git, api's integration, rest api, html</t>
+          <t>api's integration, react.js, git, html, rest api, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>git, rest api</t>
+          <t>rest api, git</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, material ui, api's integration, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>tailwind css, css, react router, react.js, react, git, material ui, api's integration, rest api, html, typescript, redux, javascript</t>
+          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
         </is>
       </c>
     </row>

--- a/output/filtered_candidates.xlsx
+++ b/output/filtered_candidates.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>redux, typescript, javascript, css, react, material ui, git, html, tailwind css</t>
+          <t>git, javascript, material ui, css, html, redux, react, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>api's integration, react.js, rest api, react router</t>
+          <t>react.js, react router, api's integration, rest api</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>redux, react.js, typescript, javascript, css, react, material ui, git, tailwind css</t>
+          <t>git, javascript, material ui, css, redux, react, react.js, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>redux, react.js, typescript, javascript, css, react, material ui, git, tailwind css</t>
+          <t>git, javascript, material ui, css, redux, react, react.js, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>api's integration, html, rest api, react router</t>
+          <t>react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>redux, react.js, typescript, javascript, css, react, git, tailwind css</t>
+          <t>git, javascript, css, redux, react, react.js, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>api's integration, html, material ui, rest api, react router</t>
+          <t>material ui, react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>redux, react.js, typescript, javascript, css, react, git, tailwind css</t>
+          <t>git, javascript, css, redux, react, react.js, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>api's integration, html, material ui, rest api, react router</t>
+          <t>material ui, react router, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>react.js, javascript, css, react, material ui, git, tailwind css</t>
+          <t>git, javascript, material ui, css, react, react.js, tailwind css</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>api's integration, typescript, redux, html, rest api, react router</t>
+          <t>react router, api's integration, typescript, redux, rest api, html</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>react.js, git, typescript, react, material ui, javascript, tailwind css, css</t>
+          <t>javascript, git, react, material ui, react.js, css, typescript, tailwind css</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>api's integration, redux, html, rest api, react router</t>
+          <t>react router, api's integration, redux, rest api, html</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>api's integration, redux, react, material ui, tailwind css, css</t>
+          <t>redux, material ui, react, css, api's integration, tailwind css</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>react.js, git, typescript, html, javascript, rest api, react router</t>
+          <t>javascript, git, react.js, react router, typescript, rest api, html</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>react.js, git, react, html, javascript, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, tailwind css, html</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>api's integration, typescript, redux, material ui, rest api, react router</t>
+          <t>material ui, react router, api's integration, typescript, redux, rest api</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>react.js, redux, react, html, javascript, css</t>
+          <t>javascript, react, react.js, css, redux, html</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>api's integration, git, typescript, material ui, rest api, react router, tailwind css</t>
+          <t>git, material ui, react router, tailwind css, api's integration, typescript, rest api</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>javascript, rest api, git</t>
+          <t>git, javascript, rest api</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>api's integration, react.js, typescript, redux, react, html, material ui, react router, tailwind css, css</t>
+          <t>react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, html</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>javascript, rest api, git</t>
+          <t>git, javascript, rest api</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>api's integration, react.js, typescript, redux, react, html, material ui, react router, tailwind css, css</t>
+          <t>react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, html</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>redux, typescript, javascript, react, material ui</t>
+          <t>javascript, material ui, redux, react, typescript</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, html, rest api, react router, tailwind css, css</t>
+          <t>git, react.js, css, react router, tailwind css, api's integration, rest api, html</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>api's integration, react.js, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
+          <t>javascript, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, rest api, html</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, html</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>rest api, git</t>
+          <t>git, rest api</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>api's integration, react.js, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
+          <t>javascript, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, html</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, react router, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, html</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, rest api, html</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, rest api, html</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>api's integration, react.js, git, typescript, redux, react, html, material ui, javascript, rest api, react router, tailwind css, css</t>
+          <t>javascript, git, react, react.js, css, material ui, react router, tailwind css, api's integration, typescript, redux, rest api, html</t>
         </is>
       </c>
     </row>
